--- a/data/trans_camb/P16A_n_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 19,9</t>
+          <t>10,95; 19,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,1</t>
+          <t>4,55; 13,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 22,23</t>
+          <t>12,26; 22,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,95</t>
+          <t>10,18; 17,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 16,5</t>
+          <t>7,9; 16,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 23,82</t>
+          <t>16,18; 23,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 17,46</t>
+          <t>12,1; 17,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,85</t>
+          <t>7,73; 14,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,43</t>
+          <t>16,18; 22,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,09; 63,53</t>
+          <t>30,97; 62,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 40,96</t>
+          <t>12,85; 43,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 69,56</t>
+          <t>34,66; 71,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,29; 39,12</t>
+          <t>20,42; 38,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 36,64</t>
+          <t>15,71; 35,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,73; 52,4</t>
+          <t>32,5; 51,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,01; 43,52</t>
+          <t>28,13; 44,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,84; 34,63</t>
+          <t>17,91; 34,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,13; 55,93</t>
+          <t>37,96; 56,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,77</t>
+          <t>5,1; 9,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,35</t>
+          <t>5,99; 10,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 17,96</t>
+          <t>6,59; 17,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,13</t>
+          <t>7,1; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 11,23</t>
+          <t>5,83; 11,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 37,32</t>
+          <t>14,09; 36,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,26</t>
+          <t>6,64; 10,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,16</t>
+          <t>6,68; 10,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,9; 28,0</t>
+          <t>12,49; 27,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,51; 115,45</t>
+          <t>48,24; 113,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,21; 123,59</t>
+          <t>55,74; 122,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,06; 203,6</t>
+          <t>71,74; 199,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,27; 78,3</t>
+          <t>35,55; 80,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,83; 67,57</t>
+          <t>30,11; 67,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,04; 215,85</t>
+          <t>76,55; 228,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,92; 79,8</t>
+          <t>45,64; 82,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,75; 79,68</t>
+          <t>46,55; 81,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,39; 211,05</t>
+          <t>88,31; 204,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,26</t>
+          <t>-3,35; 5,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 9,16</t>
+          <t>0,08; 9,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,96</t>
+          <t>7,7; 16,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 9,34</t>
+          <t>-1,83; 9,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 4,56</t>
+          <t>-5,48; 4,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,8</t>
+          <t>3,9; 13,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,51</t>
+          <t>-1,26; 5,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,63</t>
+          <t>-1,1; 5,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 14,05</t>
+          <t>7,51; 13,86</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 52,02</t>
+          <t>-24,51; 56,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 91,52</t>
+          <t>-0,15; 93,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56,37; 173,52</t>
+          <t>51,4; 162,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 54,73</t>
+          <t>-8,82; 51,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 27,22</t>
+          <t>-24,2; 28,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,96; 83,28</t>
+          <t>16,94; 81,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 38,28</t>
+          <t>-7,5; 39,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 40,17</t>
+          <t>-6,32; 39,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,22; 100,79</t>
+          <t>43,06; 100,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,91</t>
+          <t>5,83; 9,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,68</t>
+          <t>3,59; 7,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,42</t>
+          <t>4,09; 13,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,45</t>
+          <t>7,89; 12,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,38</t>
+          <t>2,64; 7,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 24,39</t>
+          <t>9,2; 24,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,77</t>
+          <t>7,55; 10,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,83</t>
+          <t>3,73; 6,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 17,94</t>
+          <t>8,25; 17,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,66; 59,93</t>
+          <t>30,9; 58,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 46,47</t>
+          <t>19,47; 44,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,96; 79,82</t>
+          <t>26,17; 78,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,68; 43,45</t>
+          <t>25,63; 43,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,87; 25,87</t>
+          <t>8,41; 26,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,44; 82,44</t>
+          <t>30,39; 85,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,63; 46,78</t>
+          <t>30,46; 46,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,61; 29,58</t>
+          <t>15,16; 29,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,51; 75,74</t>
+          <t>33,72; 74,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,19</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,18</t>
+          <t>19,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>17,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 19,52</t>
+          <t>10,64; 19,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,31</t>
+          <t>4,48; 13,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 22,3</t>
+          <t>8,61; 18,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,74</t>
+          <t>10,0; 17,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 16,31</t>
+          <t>7,63; 16,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 23,69</t>
+          <t>15,52; 23,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,96</t>
+          <t>11,73; 17,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 14,02</t>
+          <t>7,48; 13,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 22,56</t>
+          <t>14,2; 20,39</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,97; 62,86</t>
+          <t>29,45; 62,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 43,07</t>
+          <t>12,55; 42,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,66; 71,79</t>
+          <t>24,39; 60,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 38,71</t>
+          <t>20,01; 39,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 35,67</t>
+          <t>15,42; 35,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 51,74</t>
+          <t>31,33; 51,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,13; 44,81</t>
+          <t>27,61; 44,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 34,65</t>
+          <t>17,82; 35,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,96; 56,53</t>
+          <t>33,33; 51,17</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>17,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>16,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,79</t>
+          <t>16,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,52</t>
+          <t>5,11; 9,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,37</t>
+          <t>5,92; 10,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 17,77</t>
+          <t>14,78; 19,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,35</t>
+          <t>7,37; 13,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,2</t>
+          <t>5,91; 11,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 36,7</t>
+          <t>13,43; 18,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,37</t>
+          <t>6,73; 10,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,26</t>
+          <t>6,43; 10,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 27,73</t>
+          <t>14,86; 18,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149,2%</t>
+          <t>180,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>119,26%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>131,23%</t>
+          <t>123,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 113,0</t>
+          <t>48,92; 111,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,74; 122,82</t>
+          <t>56,15; 123,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,74; 199,22</t>
+          <t>140,55; 231,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,55; 80,45</t>
+          <t>37,94; 78,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,11; 67,32</t>
+          <t>29,8; 70,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,55; 228,46</t>
+          <t>68,22; 115,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,64; 82,01</t>
+          <t>46,67; 82,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,55; 81,14</t>
+          <t>44,27; 80,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,31; 204,01</t>
+          <t>101,86; 147,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,38</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,01</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,99</t>
+          <t>11,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,63</t>
+          <t>-3,63; 5,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,2</t>
+          <t>0,26; 9,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 16,59</t>
+          <t>8,11; 16,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 9,1</t>
+          <t>-2,49; 8,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,68</t>
+          <t>-5,5; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 13,65</t>
+          <t>4,61; 14,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,62</t>
+          <t>-1,28; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,49</t>
+          <t>-1,14; 5,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,86</t>
+          <t>8,35; 14,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101,21%</t>
+          <t>103,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 56,73</t>
+          <t>-24,77; 49,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 93,07</t>
+          <t>1,52; 86,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,4; 162,76</t>
+          <t>54,23; 172,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 51,99</t>
+          <t>-11,48; 48,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 28,19</t>
+          <t>-24,73; 28,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 81,46</t>
+          <t>20,25; 85,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 39,78</t>
+          <t>-7,45; 39,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 39,23</t>
+          <t>-6,82; 42,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,06; 100,79</t>
+          <t>48,72; 108,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>12,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,84</t>
+          <t>5,77; 9,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,27</t>
+          <t>3,58; 7,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,09</t>
+          <t>9,97; 14,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,52</t>
+          <t>7,82; 12,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,65</t>
+          <t>2,84; 7,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 24,67</t>
+          <t>8,44; 12,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,55</t>
+          <t>7,53; 10,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,82</t>
+          <t>3,9; 6,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 17,65</t>
+          <t>9,95; 13,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,9; 58,47</t>
+          <t>31,13; 60,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,47; 44,01</t>
+          <t>19,64; 45,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,17; 78,18</t>
+          <t>53,61; 85,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,63; 43,66</t>
+          <t>25,38; 43,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 26,84</t>
+          <t>8,98; 25,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,39; 85,58</t>
+          <t>27,27; 44,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,46; 46,11</t>
+          <t>30,82; 46,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,16; 29,46</t>
+          <t>16,03; 30,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,72; 74,12</t>
+          <t>40,92; 57,36</t>
         </is>
       </c>
     </row>
